--- a/Result/checksun_type/天然瓦斯供應.xlsx
+++ b/Result/checksun_type/天然瓦斯供應.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>33.84</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>33.8</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>177061.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>130125.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>130125.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>195896.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-57981.07476140757</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>177061</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>177061.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>33.81</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>33.8</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>33.8</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>33800.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>154563.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>154563.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>224926.1</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>0</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-62893.99127868772</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>33800</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>33800.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>33.72000000000001</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>33.63</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>33.81</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>69491.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>207982.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>207982</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>329614.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>0</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-52316.8366148491</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>69491</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>69491.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>33.66</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>33.81</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>233950.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>209008.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>209008.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>0</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-39162.19293026358</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>233950</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>233950.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>33.6</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.61</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>33.81</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.61</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>33.81</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>136327.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>264025.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>264025.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>0</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-36591.80220477487</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>136327</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>136327.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>33.59</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.62</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>33.82</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>299250.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>261667.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>261667</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>0</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-21153.35823247762</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>299250</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>299250.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>33.61</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.62</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.62</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>33.82</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>300892.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>295288.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>295288.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>0</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-15798.99690660735</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>300892</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>300892.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.59</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>33.84</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>33.84</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>74622.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>451246.4</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>451246.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>0</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-7761.587980128126</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>74622</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>74622.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.52999999999999</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.65</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.65</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>509038.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>0</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>0</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>28240.83862841816</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>509038</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>509038.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.48</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>33.86</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>33.86</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>124533.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>0</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>0</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>32119.70383246941</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>124533</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>124533.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>33.52</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>33.85</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>33.85</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>467358.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>0</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>0</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>77710.77184424025</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>467358</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>467358.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>49.7</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>49.82</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>49.82</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>298997.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>377834.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>377834.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>558033.6</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>5638327.4</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>5638327.4</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-724316.9430808858</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>298997</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>298997.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>49.61</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>49.83</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>49.83</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>158782.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>357821.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>357821.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>608094.9</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>5639416.54</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>5639416.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-802107.1771379575</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>158782</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>158782.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>49.57000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>49.61</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>49.84</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>49.61</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>49.84</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>201625.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>453679.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>453679.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>607186.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>5643296.24</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>5643296.24</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-869566.3623217045</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>201625</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>201625.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>49.52</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>49.86</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>723960.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>760224.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>760224.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>625225.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>5640406.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>5640406</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-939471.0067869966</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>723960</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>723960.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>49.44</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>49.86</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>505807.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>734192.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>734192.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>592689.1</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>5629258.38</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>5629258.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1061746.712923592</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>505807</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>505807.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>49.47</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>49.88</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>49.88</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>198935.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>738233.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>738233</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>601936.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5619188.5</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5619188.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-1175133.231942887</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>198935</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>198935.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>49.51000000000001</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>49.62</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>49.9</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>638071.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>858368.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>858368</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>702249.2</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5641401.34</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5641401.34</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-1262265.786543919</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>638071</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>638071.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>49.55</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>49.64</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>49.64</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>49.91</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>1734349.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>760693.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>760693.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>699799.7</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5630718.54</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5630718.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-1388710.229311681</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>1734349</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>1734349.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.63</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>49.66</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>49.93</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>49.93</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>593801.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>490227.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>490227</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>606779.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5598634.64</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5598634.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-1637206.71079021</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>593801</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>593801.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>49.68</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.68</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>49.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>526009.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>451185.6</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>451185.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>579202.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5589897.14</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5589897.14</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-1811528.444659888</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>526009</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>526009.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>49.65</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.69</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>49.95</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.69</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>49.95</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>799610.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>465639.8</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>465639.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>562133.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5579519.2</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5579519.2</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-1988598.620021574</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>799610</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>799610.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>39.71</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>39.65</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>39.56</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>287649.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>338090.6</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>338090.6</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>552128.5</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>392721.34</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>392721.34</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-6451.00823621091</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>287649</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>287649.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>39.72</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>39.65</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>436960.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>508934.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>508934.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>555388.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>387105.6</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>387105.6</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>9430.455992332485</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>436960</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>436960.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>39.69</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>39.63</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>598255.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>494647.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>494647.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>540116.4</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>384223.26</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>384223.26</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>15783.85289052548</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>598255</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>598255.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>39.73</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>39.61</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>39.61</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>39.58</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>321807.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>482696.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>482696.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>494109.8</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>373870.48</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>373870.48</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>7014.817998996703</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>321807</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>321807.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>39.76000000000001</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>39.6</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>45782.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>546550.2</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>546550.2</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>471533.0</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>371203.04</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>371203.04</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>23856.52465399145</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>45782</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>45782.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>39.76000000000001</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>39.59</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>39.59</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>1141869.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>766166.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>766166.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>526980.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>370295.22</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>370295.22</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>76638.19399491278</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>1141869</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>1141869.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>39.68</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>39.57</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>365525.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>601842.2</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>601842.2</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>464143.5</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>348383.04</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>348383.04</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>31865.60755355348</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>365525</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>365525.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>39.64</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>39.55</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>39.57</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>39.57</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>538498.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>585585.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>585585.2</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>483426.2</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>346031.1</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>346031.1</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>49946.42665327049</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>538498</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>538498.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>39.63</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>39.53</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>39.53</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>39.58</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>641077.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>505523.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>505523.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>466505.5</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>341000.06</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>341000.06</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>55459.54584382084</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>641077</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>641077.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>39.62</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>39.51</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>39.51</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>39.58</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1143863.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>396515.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>396515.8</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>450916.8</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>332214.26</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>332214.26</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>50364.12519304204</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1143863</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1143863.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>39.59</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>39.5</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>39.58</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>39.5</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>39.58</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>320248.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>287795.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>287795.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>367861.3</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>309355.1</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>309355.1</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-12583.69449353631</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>320248</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>320248.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,21 +15247,17 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
+      <c r="AM35" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO35" t="inlineStr">
         <is>
           <t>30.02</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>30.02</t>
-        </is>
-      </c>
       <c r="AP35" t="inlineStr">
         <is>
           <t>58.21</t>
@@ -15500,20 +15298,16 @@
           <t>1753179.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>3099087.8</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>3099087.8</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>3247047.5</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>2731132.78</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>2731132.78</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>47631.67130534118</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>1753179</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>1753179.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>30.01</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>30</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>4231256.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>3781788.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>3781788.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>3359645.4</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>2817563.1</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>2817563.1</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>189402.6909036138</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>4231256</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>4231256.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>30</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>2289012.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>3639353.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>3639353</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>3093769.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>2784958.16</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>2784958.16</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>119660.0870831595</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>2289012</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>2289012.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>30.09</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>30</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>30</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>2580196.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>3723706.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>3723706</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>2965811.0</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>2785701.92</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>2785701.92</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>223851.7928009694</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>2580196</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>2580196.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>30.07</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>29.99</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>30</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>4641796.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>3720986.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>3720986.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>3023641.1</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>2746042.68</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>2746042.68</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>333504.0940835206</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>4641796</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>4641796.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>30.07</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>29.99</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>30.01</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>30.01</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>5166681.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>3395007.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>3395007.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>2744126.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>2696240.56</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>2696240.56</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>257353.6639841818</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>5166681</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>5166681.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>30.05</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>29.98</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>29.98</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>30</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>3519080.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>2937502.6</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>2937502.6</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>2515927.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>2618281.24</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>2618281.24</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>83138.45441426337</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>3519080</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>3519080.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>30.03</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>29.97</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>29.97</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>30</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>2710777.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>2548186.8</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>2548186.8</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>2399896.1</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>2563741.24</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>2563741.24</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>7819.031656727195</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>2710777</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>2710777.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>30.01</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>30</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>2566598.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>2207916.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>2207916</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>2484778.7</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>2527194.48</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>2527194.48</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-13455.50198463583</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>2566598</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>2566598.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>30.01</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>29.96</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>29.96</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>30</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>3011900.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>2326295.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>2326295.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>2331062.6</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>2499891.9</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>2499891.9</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-27919.38925855979</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>3011900</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>3011900.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>29.98</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>29.95</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>29.95</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>30</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>2879158.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>2093245.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>2093245.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>2332730.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>2466519.8</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>2466519.8</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-95295.89289064566</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>2879158</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>2879158.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>58.24000000000001</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>58.42</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>59.41</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>59.41</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>66.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>0</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>0</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-83.72556439662594</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>66</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>58.24000000000001</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>59.47</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>59.47</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>59.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>0</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>0</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-85.16309856718794</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>59</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>59.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>58.0</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>58.46</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>59.5</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>58.46</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>59.5</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>237.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>0</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>0</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-83.42517957630557</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>237</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>237.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>58.06</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>58.5</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>59.56</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>59.56</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>296.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>0</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>0</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-97.03439603303408</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>296</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>296.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>58.16</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>58.55</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>59.62</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>58.55</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>59.62</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>0</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>0</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-124.6263260563545</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>0</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>58.23999999999999</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>58.65</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>59.68</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>59.68</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>61.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>0</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>0</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-124.6263260563545</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>61</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>61.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>58.32000000000001</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>58.76</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>59.73</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>58.76</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>59.73</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>305.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>0</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>0</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-128.3232347791001</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>305</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>305.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>58.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>58.86</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>59.8</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>58.86</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>59.8</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>0</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>0</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-155.164417426626</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>2</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>58.5</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>58.89</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>59.85</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>58.89</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>59.85</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>0</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>0</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-150.0945564094788</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>0</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>58.6</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>58.9</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>59.89</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>58.9</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>59.89</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>0</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>0</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-150.0945564094788</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>1</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>58.5</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>58.91</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>59.95</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>59.95</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>0</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>0</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-134.5468448101109</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>0</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>43.29000000000001</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>43.18</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>41.78</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>41.78</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>1536.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>2626.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>2626.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>3188.1</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>2786.64</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>2786.64</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-385.3951395347549</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>1536</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>1536.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>43.42</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>43.06</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>41.74</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>43.06</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>41.74</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>2949.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>3070.4</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>3070.4</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>3448.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>2772.3</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>2772.3</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-290.2312722836427</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>2949</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>2949.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>43.62</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>42.95</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>41.71</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>42.95</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>41.71</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>1698.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>2972.6</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>2972.6</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>3504.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>2735.62</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>2735.62</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-295.3103450576386</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>1698</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>1698.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>43.82</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>42.82</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>41.68</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>41.68</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>4301.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>3233.6</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>3233.6</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>3664.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>2726.18</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>2726.18</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-157.9836509827169</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>4301</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>4301.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>43.94</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>42.68</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>41.66</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>41.66</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>2650.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>2852.0</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>2852</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>3631.4</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>2693.88</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>2693.88</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-235.0532433405888</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>2650</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>2650.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>43.93</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>42.5</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>41.63</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>41.63</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>3754.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>3749.4</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>3749.4</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>3595.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>2655.44</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>2655.44</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-159.8650451610993</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>3754</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>3754.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>42.33</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>41.6</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>42.33</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>41.6</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>2460.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>3826.8</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>3826.8</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>3932.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>2588.08</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>2588.08</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-165.0295818632176</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>2460</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>2460.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>43.69</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>42.16</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>41.56</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>42.16</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>41.56</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>3003.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>4037.2</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>4037.2</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>5554.7</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>2559.24</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>2559.24</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-27.87072065684333</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>3003</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>3003.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>43.4</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>41.97</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>41.52</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>41.97</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>41.52</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2393.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>4094.4</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>4094.4</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>6506.5</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>2535.84</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>2535.84</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>110.8873210900074</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2393</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2393.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>43.13</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>41.48</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>41.48</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>7137.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>4410.8</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>4410.8</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>6573.4</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>2508.68</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>2508.68</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>370.5099764037222</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>7137</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>7137.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>43.08</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>41.63</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>41.44</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>41.44</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>4141.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3441.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3441.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>6104.1</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>2389.1</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>2389.1</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>219.8812705517539</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>4141</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>4141.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>

--- a/Result/checksun_type/天然瓦斯供應.xlsx
+++ b/Result/checksun_type/天然瓦斯供應.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ67"/>
+  <dimension ref="A1:CJ66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5178,17 +5178,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>9926</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>15.15</t>
+          <t>7.179</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-19.00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5228,37 +5228,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-04-25 00:00:00</t>
+          <t>2025-07-01 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-06-13 00:00:00</t>
+          <t>2025-07-08 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2025-02-21 00:00:00</t>
+          <t>2025-06-06 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-03-31 00:00:00</t>
+          <t>2025-06-18 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>35.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>34.45</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>35.35</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -5283,27 +5283,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-6.42</t>
+          <t>-4.42</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,124 +5319,124 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>86.11</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.57</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>33.52999999999999</t>
+          <t>49.79000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>33.65</v>
+        <v>49.63</v>
       </c>
       <c r="AN12" t="n">
-        <v>33.85</v>
+        <v>49.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>49.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>100.10</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.78</t>
+          <t>-108.22</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/11/19</t>
+          <t>2025/11/20</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>1042904.69527897</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>509038.0</t>
+          <t>356809.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>308831.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>381255.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>5642450.84</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-72424</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34072.80050817349</t>
+          <t>-917576.0231952389</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>28240.83862841816</t>
+          <t>-510374.3157262389</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>509038.0</t>
+          <t>356809.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5446,27 +5446,27 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>35.2</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>2025/05/20</t>
+          <t>2025/05/16</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>欣高</t>
+          <t>新海</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
@@ -5481,27 +5481,27 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>9.386716078030704</t>
+          <t>-1.973702452847977</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>15.82518130059685</t>
+          <t>2.915798176461684</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-24.97116764514025</t>
+          <t>5.779024278433221</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,52 +5511,52 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.42</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>14.61%</t>
+          <t>28.40%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>9.06%</t>
+          <t>19.36%</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>天然氣78.00%、導管裝置22.00% (2024年)</t>
+          <t>天然氣72.76%、裝置16.18%、其他10.74%、電信0.33% (2024年)</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>欣高-油電燃氣業-上市</t>
+          <t>新海-油電燃氣業-上市</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5566,27 +5566,27 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>33.8</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>33.25</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>33.55</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>23.26</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5638,14 +5638,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>-0.5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>-46.48</t>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6498,7 +6498,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6948,7 +6948,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7034,12 +7034,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7464,12 +7464,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7980,7 +7980,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8526,7 +8526,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9078,7 +9078,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9098,7 +9098,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9508,7 +9508,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>2829760.309012875</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.83</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9903,22 +9903,22 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>9918</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>12.004</t>
+          <t>12.485</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,7 +9938,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9948,7 +9948,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-19.21</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9963,32 +9963,32 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2025-07-01 00:00:00</t>
+          <t>2025-08-15 00:00:00</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2025-07-08 00:00:00</t>
+          <t>2025-08-19 00:00:00</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2025-06-06 00:00:00</t>
+          <t>2025-08-07 00:00:00</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-06-18 00:00:00</t>
+          <t>2025-08-08 00:00:00</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>40.45</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -10013,27 +10013,27 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-5.19</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>22.70</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,114 +10059,114 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>26.67</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>49.63</t>
+          <t>39.66</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>49.66</v>
+        <v>39.67</v>
       </c>
       <c r="AN23" t="n">
-        <v>49.93</v>
+        <v>39.58</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>50.07</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-54.75</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-120.07</t>
+          <t>-88.84</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/11/20</t>
+          <t>2025/10/28</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>2833047.625358166</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>593801.0</t>
+          <t>493797.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>490227</v>
+        <v>574348.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>606779.8</t>
+          <t>534498.0</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>5598634.64</v>
+        <v>415264.5</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-116552</t>
+          <t>39850</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-1686595.306224994</t>
+          <t>24629.2790409858</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-1637206.71079021</t>
+          <t>27102.78733241127</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>593801.0</t>
+          <t>493797.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10176,27 +10176,27 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>39.6</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>2025/05/16</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>新海</t>
+          <t>欣天然</t>
         </is>
       </c>
       <c r="BK23" t="inlineStr">
@@ -10216,77 +10216,77 @@
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-1.973702452847977</t>
+          <t>2.047031841062759</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>2.915798176461684</t>
+          <t>-2.290843754901821</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>5.779024278433221</t>
+          <t>4.371878666197554</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
         <is>
-          <t>28.40%</t>
+          <t>28.52%</t>
         </is>
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>19.36%</t>
+          <t>13.31%</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>8966</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
         <is>
-          <t>天然氣72.76%、裝置16.18%、其他10.74%、電信0.33% (2024年)</t>
+          <t>天然氣78.23%、裝置12.68%、其他營業收入9.09% (2024年)</t>
         </is>
       </c>
       <c r="CB23" t="inlineStr">
         <is>
-          <t>新海-油電燃氣業-上市</t>
+          <t>欣天然-油電燃氣業-上市</t>
         </is>
       </c>
       <c r="CC23" t="inlineStr">
@@ -10296,27 +10296,27 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>39.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>18.28</t>
         </is>
       </c>
       <c r="CI23" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -10479,7 +10479,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10798,7 +10798,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -10990,7 +10990,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -11339,7 +11339,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11561,12 +11561,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -11769,7 +11769,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11991,12 +11991,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -12199,7 +12199,7 @@
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -12280,7 +12280,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12421,12 +12421,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12851,12 +12851,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -13059,7 +13059,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -13489,7 +13489,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -13696,7 +13696,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13711,12 +13711,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -14000,7 +14000,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
@@ -14126,7 +14126,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -14141,12 +14141,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -14238,7 +14238,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -14349,7 +14349,7 @@
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>1095929.025641026</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>22.83</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14633,22 +14633,22 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9908</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16.187</t>
+          <t>79.032</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14668,7 +14668,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -14678,12 +14678,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>8.36</t>
+          <t>-19.51</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -14693,77 +14693,77 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>2025-08-15 00:00:00</t>
+          <t>2025-11-27 00:00:00</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2025-08-19 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2025-08-07 00:00:00</t>
+          <t>2025-07-29 00:00:00</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-08-08 00:00:00</t>
+          <t>2025-07-30 00:00:00</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>31.25</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>29.43</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14774,63 +14774,63 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>39.63</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>39.53</v>
+        <v>30.04</v>
       </c>
       <c r="AN34" t="n">
-        <v>39.58</v>
+        <v>30.01</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>39.8</t>
+          <t>30.02</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>1104.49</t>
+          <t>17.06</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
@@ -14840,93 +14840,93 @@
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>-0.00</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-100.99</t>
+          <t>-88.28</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2025/10/28</t>
+          <t>2025/11/07</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>1096435.778174037</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>641077.0</t>
+          <t>2373990.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>505523.4</v>
+        <v>2450937</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>466505.5</t>
+          <t>3045145.0</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>341000.06</v>
+        <v>2744516.72</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>39017</t>
+          <t>-594208</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>17900.94605393493</t>
+          <t>24891.16084569724</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>55459.54584382084</t>
+          <t>-92680.24498464074</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>641077.0</t>
+          <t>2373990.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>39.6</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>2025/11/18</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
         <is>
-          <t>欣天然</t>
+          <t>大台北</t>
         </is>
       </c>
       <c r="BK34" t="inlineStr">
@@ -14941,27 +14941,27 @@
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>2.047031841062759</t>
+          <t>1.455111192459046</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>-2.290843754901821</t>
+          <t>-0.7334677764714127</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr">
         <is>
-          <t>4.371878666197554</t>
+          <t>2.820186761949039</t>
         </is>
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14971,52 +14971,52 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>22.86</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
         <is>
-          <t>28.52%</t>
+          <t>24.07%</t>
         </is>
       </c>
       <c r="BX34" t="inlineStr">
         <is>
-          <t>13.31%</t>
+          <t>13.29%</t>
         </is>
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
         <is>
-          <t>天然氣78.23%、裝置12.68%、其他營業收入9.09% (2024年)</t>
+          <t>氣體70.48%、裝置17.76%、租賃8.48%、通信1.91%、器具0.93%、勞務0.44% (2024年)</t>
         </is>
       </c>
       <c r="CB34" t="inlineStr">
         <is>
-          <t>欣天然-油電燃氣業-上市</t>
+          <t>大台北-油電燃氣業-上市</t>
         </is>
       </c>
       <c r="CC34" t="inlineStr">
@@ -15026,27 +15026,27 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>30.15</t>
         </is>
       </c>
       <c r="CF34" t="inlineStr">
         <is>
-          <t>39.2</t>
+          <t>29.95</t>
         </is>
       </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>39.85</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">
         <is>
-          <t>18.28</t>
+          <t>27.35</t>
         </is>
       </c>
       <c r="CI34" t="inlineStr">
@@ -15098,14 +15098,14 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>-0.33</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>-20.95</t>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -15209,7 +15209,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
@@ -15406,7 +15406,7 @@
       </c>
       <c r="BT35" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU35" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="BV35" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW35" t="inlineStr">
@@ -15431,12 +15431,12 @@
       </c>
       <c r="BY35" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ35" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA35" t="inlineStr">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -15558,7 +15558,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -15639,7 +15639,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -15720,7 +15720,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -15761,7 +15761,7 @@
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>2025-11-29</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="BT36" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU36" t="inlineStr">
@@ -15846,7 +15846,7 @@
       </c>
       <c r="BV36" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW36" t="inlineStr">
@@ -15861,12 +15861,12 @@
       </c>
       <c r="BY36" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ36" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA36" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -15988,7 +15988,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -16069,7 +16069,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -16150,7 +16150,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -16266,7 +16266,7 @@
       </c>
       <c r="BT37" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU37" t="inlineStr">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="BV37" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW37" t="inlineStr">
@@ -16291,12 +16291,12 @@
       </c>
       <c r="BY37" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ37" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA37" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -16580,7 +16580,7 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="BT38" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU38" t="inlineStr">
@@ -16706,7 +16706,7 @@
       </c>
       <c r="BV38" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW38" t="inlineStr">
@@ -16721,12 +16721,12 @@
       </c>
       <c r="BY38" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ38" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA38" t="inlineStr">
@@ -16818,7 +16818,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -16848,7 +16848,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -16929,7 +16929,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -17126,7 +17126,7 @@
       </c>
       <c r="BT39" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU39" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="BV39" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW39" t="inlineStr">
@@ -17151,12 +17151,12 @@
       </c>
       <c r="BY39" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ39" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA39" t="inlineStr">
@@ -17248,7 +17248,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -17359,7 +17359,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -17556,7 +17556,7 @@
       </c>
       <c r="BT40" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU40" t="inlineStr">
@@ -17566,7 +17566,7 @@
       </c>
       <c r="BV40" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW40" t="inlineStr">
@@ -17581,12 +17581,12 @@
       </c>
       <c r="BY40" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ40" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA40" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -17870,7 +17870,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="BT41" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU41" t="inlineStr">
@@ -17996,7 +17996,7 @@
       </c>
       <c r="BV41" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW41" t="inlineStr">
@@ -18011,12 +18011,12 @@
       </c>
       <c r="BY41" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ41" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA41" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -18138,7 +18138,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -18219,7 +18219,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="BT42" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU42" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="BV42" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW42" t="inlineStr">
@@ -18441,12 +18441,12 @@
       </c>
       <c r="BY42" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ42" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA42" t="inlineStr">
@@ -18538,7 +18538,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -18568,7 +18568,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -18649,7 +18649,7 @@
       </c>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -18730,7 +18730,7 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
@@ -18836,7 +18836,7 @@
       </c>
       <c r="BR43" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS43" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="BT43" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU43" t="inlineStr">
@@ -18856,7 +18856,7 @@
       </c>
       <c r="BV43" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW43" t="inlineStr">
@@ -18871,12 +18871,12 @@
       </c>
       <c r="BY43" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ43" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA43" t="inlineStr">
@@ -18968,7 +18968,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -18998,7 +18998,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -19079,7 +19079,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -19160,7 +19160,7 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>5343800.463675214</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
@@ -19276,7 +19276,7 @@
       </c>
       <c r="BT44" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="BU44" t="inlineStr">
@@ -19286,7 +19286,7 @@
       </c>
       <c r="BV44" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>17.57</t>
         </is>
       </c>
       <c r="BW44" t="inlineStr">
@@ -19301,12 +19301,12 @@
       </c>
       <c r="BY44" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>27.82</t>
         </is>
       </c>
       <c r="BZ44" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15517</t>
         </is>
       </c>
       <c r="CA44" t="inlineStr">
@@ -19368,17 +19368,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>85.621</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -19418,37 +19418,37 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2025-11-27 00:00:00</t>
+          <t>2025-09-23 00:00:00</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2025-11-29 00:00:00</t>
+          <t>2025-10-03 00:00:00</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>2025-07-29 00:00:00</t>
+          <t>2025-08-18 00:00:00</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00</t>
+          <t>2025-08-20 00:00:00</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60.1</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>60.7</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
@@ -19473,27 +19473,27 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.83</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
           <t>0.00</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>7.07</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>0.17</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
@@ -19509,124 +19509,124 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>88.89</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>30.01</t>
+          <t>58.36</t>
         </is>
       </c>
       <c r="AM45" t="n">
-        <v>29.96</v>
+        <v>58.28</v>
       </c>
       <c r="AN45" t="n">
-        <v>30</v>
+        <v>59.25</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>59.97</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>102.50</t>
+          <t>20.41</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>-105.84</t>
+          <t>-141.53</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>2025/11/07</t>
+          <t>2025/11/24</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>5346343.709700428</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>2566598.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AX45" t="n">
-        <v>2207916</v>
+        <v>0</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>2484778.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ45" t="n">
-        <v>2527194.48</v>
+        <v>0</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>-276862</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>-63857.18064968136</t>
+          <t>-84.55336826924952</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>-13455.50198463583</t>
+          <t>-69.2369509960443</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>2566598.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
@@ -19636,27 +19636,27 @@
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/08/13</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-6.71</t>
         </is>
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr">
         <is>
-          <t>大台北</t>
+          <t>欣泰</t>
         </is>
       </c>
       <c r="BK45" t="inlineStr">
@@ -19666,32 +19666,32 @@
       </c>
       <c r="BL45" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="BM45" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="BN45" t="inlineStr">
         <is>
-          <t>1.455111192459046</t>
+          <t>3.043583375458801</t>
         </is>
       </c>
       <c r="BO45" t="inlineStr">
         <is>
-          <t>-0.7334677764714127</t>
+          <t>0.1409720234611622</t>
         </is>
       </c>
       <c r="BP45" t="inlineStr">
         <is>
-          <t>2.820186761949039</t>
+          <t>14.5435927704594</t>
         </is>
       </c>
       <c r="BQ45" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR45" t="inlineStr">
@@ -19701,82 +19701,82 @@
       </c>
       <c r="BS45" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="BT45" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU45" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>4.26</t>
         </is>
       </c>
       <c r="BV45" t="inlineStr">
         <is>
-          <t>17.63</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW45" t="inlineStr">
         <is>
-          <t>24.07%</t>
+          <t>17.54%</t>
         </is>
       </c>
       <c r="BX45" t="inlineStr">
         <is>
-          <t>13.29%</t>
+          <t>11.48%</t>
         </is>
       </c>
       <c r="BY45" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ45" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA45" t="inlineStr">
         <is>
-          <t>氣體70.48%、裝置17.76%、租賃8.48%、通信1.91%、器具0.93%、勞務0.44% (2024年)</t>
+          <t>天然氣81.13%、供氣管線安裝18.87% (2024年)</t>
         </is>
       </c>
       <c r="CB45" t="inlineStr">
         <is>
-          <t>大台北-油電燃氣業-上市</t>
+          <t>欣泰-油電燃氣業-上櫃</t>
         </is>
       </c>
       <c r="CC45" t="inlineStr">
         <is>
-          <t>油電燃氣業右下上市</t>
+          <t>油電燃氣業右下上櫃</t>
         </is>
       </c>
       <c r="CD45" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CE45" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CF45" t="inlineStr">
         <is>
-          <t>29.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CG45" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="CH45" t="inlineStr">
         <is>
-          <t>27.35</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="CI45" t="inlineStr">
@@ -19828,12 +19828,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -19934,12 +19934,12 @@
       <c r="AC46" t="inlineStr"/>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="BT46" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU46" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="BV46" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW46" t="inlineStr">
@@ -20161,12 +20161,12 @@
       </c>
       <c r="BY46" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ46" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA46" t="inlineStr">
@@ -20258,12 +20258,12 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -20364,12 +20364,12 @@
       <c r="AC47" t="inlineStr"/>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -20450,7 +20450,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -20566,7 +20566,7 @@
       </c>
       <c r="BT47" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU47" t="inlineStr">
@@ -20576,7 +20576,7 @@
       </c>
       <c r="BV47" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW47" t="inlineStr">
@@ -20591,12 +20591,12 @@
       </c>
       <c r="BY47" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ47" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA47" t="inlineStr">
@@ -20688,12 +20688,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>0.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-1.0</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -20794,12 +20794,12 @@
       <c r="AC48" t="inlineStr"/>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -20880,7 +20880,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -20996,7 +20996,7 @@
       </c>
       <c r="BT48" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU48" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="BV48" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW48" t="inlineStr">
@@ -21021,12 +21021,12 @@
       </c>
       <c r="BY48" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ48" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA48" t="inlineStr">
@@ -21118,12 +21118,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -21224,12 +21224,12 @@
       <c r="AC49" t="inlineStr"/>
       <c r="AD49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="BT49" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU49" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="BV49" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW49" t="inlineStr">
@@ -21451,12 +21451,12 @@
       </c>
       <c r="BY49" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ49" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA49" t="inlineStr">
@@ -21548,12 +21548,12 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -21654,12 +21654,12 @@
       <c r="AC50" t="inlineStr"/>
       <c r="AD50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -21740,7 +21740,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="BT50" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU50" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="BV50" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW50" t="inlineStr">
@@ -21881,12 +21881,12 @@
       </c>
       <c r="BY50" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ50" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA50" t="inlineStr">
@@ -21978,12 +21978,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -22084,12 +22084,12 @@
       <c r="AC51" t="inlineStr"/>
       <c r="AD51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -22170,7 +22170,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="BT51" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU51" t="inlineStr">
@@ -22296,7 +22296,7 @@
       </c>
       <c r="BV51" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW51" t="inlineStr">
@@ -22311,12 +22311,12 @@
       </c>
       <c r="BY51" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ51" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA51" t="inlineStr">
@@ -22408,12 +22408,12 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>0.0</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>-1.0</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -22514,12 +22514,12 @@
       <c r="AC52" t="inlineStr"/>
       <c r="AD52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -22716,7 +22716,7 @@
       </c>
       <c r="BT52" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU52" t="inlineStr">
@@ -22726,7 +22726,7 @@
       </c>
       <c r="BV52" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW52" t="inlineStr">
@@ -22741,12 +22741,12 @@
       </c>
       <c r="BY52" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ52" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA52" t="inlineStr">
@@ -22838,12 +22838,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>0.0</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>-1.0</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -22944,12 +22944,12 @@
       <c r="AC53" t="inlineStr"/>
       <c r="AD53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="BT53" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU53" t="inlineStr">
@@ -23156,7 +23156,7 @@
       </c>
       <c r="BV53" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW53" t="inlineStr">
@@ -23171,12 +23171,12 @@
       </c>
       <c r="BY53" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ53" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA53" t="inlineStr">
@@ -23268,12 +23268,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>0.0</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>-1.0</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -23374,12 +23374,12 @@
       <c r="AC54" t="inlineStr"/>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -23576,7 +23576,7 @@
       </c>
       <c r="BT54" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU54" t="inlineStr">
@@ -23586,7 +23586,7 @@
       </c>
       <c r="BV54" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW54" t="inlineStr">
@@ -23601,12 +23601,12 @@
       </c>
       <c r="BY54" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ54" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA54" t="inlineStr">
@@ -23698,12 +23698,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -23804,12 +23804,12 @@
       <c r="AC55" t="inlineStr"/>
       <c r="AD55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -23890,7 +23890,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>1549.971810089021</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BT55" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="BU55" t="inlineStr">
@@ -24016,7 +24016,7 @@
       </c>
       <c r="BV55" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>27.29</t>
         </is>
       </c>
       <c r="BW55" t="inlineStr">
@@ -24031,12 +24031,12 @@
       </c>
       <c r="BY55" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ55" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="CA55" t="inlineStr">
@@ -24093,57 +24093,57 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>58.4</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13.85</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -24153,240 +24153,240 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2025-09-23 00:00:00</t>
+          <t>2025-12-01 00:00:00</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2025-10-03 00:00:00</t>
+          <t>2025-12-02 00:00:00</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>2025-08-18 00:00:00</t>
+          <t>2025-11-13 00:00:00</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2025-08-20 00:00:00</t>
+          <t>2025-11-24 00:00:00</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>61.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>60.1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>43.85</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>60.7</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
       <c r="AD56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>72.46</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>43.78</t>
         </is>
       </c>
       <c r="AM56" t="n">
-        <v>58.89</v>
+        <v>43.62</v>
       </c>
       <c r="AN56" t="n">
-        <v>59.85</v>
+        <v>41.96</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>60.22</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>7.44</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>-154.29</t>
+          <t>-46.31</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2025/11/24</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>1551.94279346211</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8543.0</t>
         </is>
       </c>
       <c r="AX56" t="n">
-        <v>0</v>
+        <v>3928</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3450.3</t>
         </is>
       </c>
       <c r="AZ56" t="n">
-        <v>0</v>
+        <v>3002.66</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>477</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>-56.15984919882795</t>
+          <t>-74.83861325795888</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>-150.0945564094788</t>
+          <t>231.2591026022683</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8543.0</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>2025/08/13</t>
+          <t>2025/11/11</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>-6.71</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr">
         <is>
-          <t>欣泰</t>
+          <t>欣雄</t>
         </is>
       </c>
       <c r="BK56" t="inlineStr">
@@ -24401,82 +24401,82 @@
       </c>
       <c r="BM56" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="BN56" t="inlineStr">
         <is>
-          <t>3.043583375458801</t>
+          <t>-5.013728558353754</t>
         </is>
       </c>
       <c r="BO56" t="inlineStr">
         <is>
-          <t>0.1409720234611622</t>
+          <t>8.333512919423313</t>
         </is>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>14.5435927704594</t>
+          <t>40.33084016434755</t>
         </is>
       </c>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS56" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="BT56" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU56" t="inlineStr">
         <is>
-          <t>4.26</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="BV56" t="inlineStr">
         <is>
-          <t>27.15</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW56" t="inlineStr">
         <is>
-          <t>17.54%</t>
+          <t>9.86%</t>
         </is>
       </c>
       <c r="BX56" t="inlineStr">
         <is>
-          <t>11.48%</t>
+          <t>7.44%</t>
         </is>
       </c>
       <c r="BY56" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ56" t="inlineStr">
         <is>
-          <t>9434</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA56" t="inlineStr">
         <is>
-          <t>天然氣81.13%、供氣管線安裝18.87% (2024年)</t>
+          <t>售氣91.00%、裝置及其他9.00% (2024年)</t>
         </is>
       </c>
       <c r="CB56" t="inlineStr">
         <is>
-          <t>欣泰-油電燃氣業-上櫃</t>
+          <t>欣雄-油電燃氣業-上櫃</t>
         </is>
       </c>
       <c r="CC56" t="inlineStr">
@@ -24486,27 +24486,27 @@
       </c>
       <c r="CD56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>45.35</t>
         </is>
       </c>
       <c r="CF56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CG56" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="CH56" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="CI56" t="inlineStr">
@@ -24558,12 +24558,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -24578,54 +24578,54 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V57" t="inlineStr">
         <is>
           <t>0</t>
@@ -24633,12 +24633,12 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
@@ -24664,12 +24664,12 @@
       <c r="AC57" t="inlineStr"/>
       <c r="AD57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -24745,12 +24745,12 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="BT57" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU57" t="inlineStr">
@@ -24876,7 +24876,7 @@
       </c>
       <c r="BV57" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW57" t="inlineStr">
@@ -24891,12 +24891,12 @@
       </c>
       <c r="BY57" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ57" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA57" t="inlineStr">
@@ -24988,12 +24988,12 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -25008,54 +25008,54 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V58" t="inlineStr">
         <is>
           <t>0</t>
@@ -25063,12 +25063,12 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -25094,12 +25094,12 @@
       <c r="AC58" t="inlineStr"/>
       <c r="AD58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -25175,12 +25175,12 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -25296,7 +25296,7 @@
       </c>
       <c r="BT58" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU58" t="inlineStr">
@@ -25306,7 +25306,7 @@
       </c>
       <c r="BV58" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW58" t="inlineStr">
@@ -25321,12 +25321,12 @@
       </c>
       <c r="BY58" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ58" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA58" t="inlineStr">
@@ -25418,12 +25418,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -25438,54 +25438,54 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q59" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V59" t="inlineStr">
         <is>
           <t>0</t>
@@ -25493,12 +25493,12 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -25524,12 +25524,12 @@
       <c r="AC59" t="inlineStr"/>
       <c r="AD59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -25605,12 +25605,12 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -25726,7 +25726,7 @@
       </c>
       <c r="BT59" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU59" t="inlineStr">
@@ -25736,7 +25736,7 @@
       </c>
       <c r="BV59" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW59" t="inlineStr">
@@ -25751,12 +25751,12 @@
       </c>
       <c r="BY59" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ59" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA59" t="inlineStr">
@@ -25848,12 +25848,12 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3.48</t>
+          <t>4.98</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -25868,54 +25868,54 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V60" t="inlineStr">
         <is>
           <t>0</t>
@@ -25923,12 +25923,12 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
@@ -25954,12 +25954,12 @@
       <c r="AC60" t="inlineStr"/>
       <c r="AD60" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -26035,12 +26035,12 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -26156,7 +26156,7 @@
       </c>
       <c r="BT60" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU60" t="inlineStr">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="BV60" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW60" t="inlineStr">
@@ -26181,12 +26181,12 @@
       </c>
       <c r="BY60" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ60" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA60" t="inlineStr">
@@ -26278,12 +26278,12 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -26298,54 +26298,54 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V61" t="inlineStr">
         <is>
           <t>-1.71</t>
@@ -26353,12 +26353,12 @@
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
@@ -26384,12 +26384,12 @@
       <c r="AC61" t="inlineStr"/>
       <c r="AD61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -26465,12 +26465,12 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -26586,7 +26586,7 @@
       </c>
       <c r="BT61" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU61" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="BV61" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW61" t="inlineStr">
@@ -26611,12 +26611,12 @@
       </c>
       <c r="BY61" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ61" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA61" t="inlineStr">
@@ -26708,12 +26708,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -26728,54 +26728,54 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V62" t="inlineStr">
         <is>
           <t>-1.03</t>
@@ -26783,12 +26783,12 @@
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
@@ -26814,12 +26814,12 @@
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -26895,12 +26895,12 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -27016,7 +27016,7 @@
       </c>
       <c r="BT62" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU62" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="BV62" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW62" t="inlineStr">
@@ -27041,12 +27041,12 @@
       </c>
       <c r="BY62" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ62" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA62" t="inlineStr">
@@ -27138,12 +27138,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -27158,54 +27158,54 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q63" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V63" t="inlineStr">
         <is>
           <t>0.11</t>
@@ -27213,12 +27213,12 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -27244,12 +27244,12 @@
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -27325,12 +27325,12 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -27446,7 +27446,7 @@
       </c>
       <c r="BT63" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU63" t="inlineStr">
@@ -27456,7 +27456,7 @@
       </c>
       <c r="BV63" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW63" t="inlineStr">
@@ -27471,12 +27471,12 @@
       </c>
       <c r="BY63" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ63" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA63" t="inlineStr">
@@ -27568,12 +27568,12 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -27588,54 +27588,54 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V64" t="inlineStr">
         <is>
           <t>-0.23</t>
@@ -27643,12 +27643,12 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -27674,12 +27674,12 @@
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -27755,12 +27755,12 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="BT64" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU64" t="inlineStr">
@@ -27886,7 +27886,7 @@
       </c>
       <c r="BV64" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW64" t="inlineStr">
@@ -27901,12 +27901,12 @@
       </c>
       <c r="BY64" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ64" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA64" t="inlineStr">
@@ -27998,12 +27998,12 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -28018,54 +28018,54 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V65" t="inlineStr">
         <is>
           <t>0.23</t>
@@ -28073,12 +28073,12 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
@@ -28104,12 +28104,12 @@
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -28185,12 +28185,12 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
@@ -28296,7 +28296,7 @@
       </c>
       <c r="BR65" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS65" t="inlineStr">
@@ -28306,7 +28306,7 @@
       </c>
       <c r="BT65" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU65" t="inlineStr">
@@ -28316,7 +28316,7 @@
       </c>
       <c r="BV65" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW65" t="inlineStr">
@@ -28331,12 +28331,12 @@
       </c>
       <c r="BY65" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ65" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA65" t="inlineStr">
@@ -28428,14 +28428,14 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
           <t>0.9</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="J66" t="inlineStr">
         <is>
           <t>-27.32</t>
@@ -28448,54 +28448,54 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
+          <t>2025-12-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
           <t>2025-11-13 00:00:00</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>2025-11-24 00:00:00</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
+          <t>45.2</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
           <t>43.85</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>43.85</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
         <is>
           <t>43.1</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
       <c r="V66" t="inlineStr">
         <is>
           <t>0.57</t>
@@ -28503,12 +28503,12 @@
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -28534,12 +28534,12 @@
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>189</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -28615,12 +28615,12 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2025/10/27</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>3975.062054208273</t>
+          <t>3987.653846153846</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
@@ -28736,7 +28736,7 @@
       </c>
       <c r="BT66" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="BU66" t="inlineStr">
@@ -28746,7 +28746,7 @@
       </c>
       <c r="BV66" t="inlineStr">
         <is>
-          <t>20.23</t>
+          <t>20.55</t>
         </is>
       </c>
       <c r="BW66" t="inlineStr">
@@ -28761,12 +28761,12 @@
       </c>
       <c r="BY66" t="inlineStr">
         <is>
-          <t>22.07</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BZ66" t="inlineStr">
         <is>
-          <t>14032</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="CA66" t="inlineStr">
@@ -28815,436 +28815,6 @@
         </is>
       </c>
       <c r="CJ66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>【b】</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>8908</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>55.0</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>1.12</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>-37.07</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>2025-11-13</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2025-11-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>2025-08-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>2025-08-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>43.1</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>43.85</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>42.55</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>42.25</t>
-        </is>
-      </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>0.34</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2.09</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>3.79</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13.03</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>0.94</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr"/>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>73.98</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>1.1</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>-0.62</t>
-        </is>
-      </c>
-      <c r="AL67" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="AM67" t="n">
-        <v>41.97</v>
-      </c>
-      <c r="AN67" t="n">
-        <v>41.52</v>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>41.77</t>
-        </is>
-      </c>
-      <c r="AP67" t="inlineStr">
-        <is>
-          <t>44.78</t>
-        </is>
-      </c>
-      <c r="AQ67" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="AT67" t="inlineStr">
-        <is>
-          <t>-52.29</t>
-        </is>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>2025/10/27</t>
-        </is>
-      </c>
-      <c r="AV67" t="inlineStr">
-        <is>
-          <t>3975.062054208273</t>
-        </is>
-      </c>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>2393.0</t>
-        </is>
-      </c>
-      <c r="AX67" t="n">
-        <v>4094.4</v>
-      </c>
-      <c r="AY67" t="inlineStr">
-        <is>
-          <t>6506.5</t>
-        </is>
-      </c>
-      <c r="AZ67" t="n">
-        <v>2535.84</v>
-      </c>
-      <c r="BA67" t="inlineStr">
-        <is>
-          <t>-2412</t>
-        </is>
-      </c>
-      <c r="BB67" t="inlineStr">
-        <is>
-          <t>492.2754597129861</t>
-        </is>
-      </c>
-      <c r="BC67" t="inlineStr">
-        <is>
-          <t>110.8873210900074</t>
-        </is>
-      </c>
-      <c r="BD67" t="inlineStr">
-        <is>
-          <t>2393.0</t>
-        </is>
-      </c>
-      <c r="BE67" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="BF67" t="inlineStr">
-        <is>
-          <t>42.8</t>
-        </is>
-      </c>
-      <c r="BG67" t="inlineStr">
-        <is>
-          <t>2025/11/11</t>
-        </is>
-      </c>
-      <c r="BH67" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="BI67" t="inlineStr">
-        <is>
-          <t>欣雄</t>
-        </is>
-      </c>
-      <c r="BJ67" t="inlineStr">
-        <is>
-          <t>欣雄</t>
-        </is>
-      </c>
-      <c r="BK67" t="inlineStr">
-        <is>
-          <t>油電燃氣業</t>
-        </is>
-      </c>
-      <c r="BL67" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM67" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
-      <c r="BN67" t="inlineStr">
-        <is>
-          <t>-5.013728558353754</t>
-        </is>
-      </c>
-      <c r="BO67" t="inlineStr">
-        <is>
-          <t>8.333512919423313</t>
-        </is>
-      </c>
-      <c r="BP67" t="inlineStr">
-        <is>
-          <t>40.33084016434755</t>
-        </is>
-      </c>
-      <c r="BQ67" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR67" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS67" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="BT67" t="inlineStr">
-        <is>
-          <t>3.6</t>
-        </is>
-      </c>
-      <c r="BU67" t="inlineStr">
-        <is>
-          <t>7.99</t>
-        </is>
-      </c>
-      <c r="BV67" t="inlineStr">
-        <is>
-          <t>20.23</t>
-        </is>
-      </c>
-      <c r="BW67" t="inlineStr">
-        <is>
-          <t>9.86%</t>
-        </is>
-      </c>
-      <c r="BX67" t="inlineStr">
-        <is>
-          <t>7.44%</t>
-        </is>
-      </c>
-      <c r="BY67" t="inlineStr">
-        <is>
-          <t>22.07</t>
-        </is>
-      </c>
-      <c r="BZ67" t="inlineStr">
-        <is>
-          <t>14032</t>
-        </is>
-      </c>
-      <c r="CA67" t="inlineStr">
-        <is>
-          <t>售氣91.00%、裝置及其他9.00% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB67" t="inlineStr">
-        <is>
-          <t>欣雄-油電燃氣業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC67" t="inlineStr">
-        <is>
-          <t>油電燃氣業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD67" t="inlineStr">
-        <is>
-          <t>43.35</t>
-        </is>
-      </c>
-      <c r="CE67" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="CF67" t="inlineStr">
-        <is>
-          <t>43.2</t>
-        </is>
-      </c>
-      <c r="CG67" t="inlineStr">
-        <is>
-          <t>44.0</t>
-        </is>
-      </c>
-      <c r="CH67" t="inlineStr">
-        <is>
-          <t>13.67</t>
-        </is>
-      </c>
-      <c r="CI67" t="inlineStr">
-        <is>
-          <t>** 油電燃氣 - 天然瓦斯供應</t>
-        </is>
-      </c>
-      <c r="CJ67" t="inlineStr">
         <is>
           <t>False</t>
         </is>
